--- a/huaibei_rent_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/huaibei_rent_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB14"/>
+  <dimension ref="A1:BD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -460,34 +460,36 @@
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="15" customWidth="1" min="25" max="25"/>
     <col width="19" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="6" customWidth="1" min="34" max="34"/>
-    <col width="6" customWidth="1" min="35" max="35"/>
-    <col width="16" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="30" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="6" customWidth="1" min="36" max="36"/>
+    <col width="6" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="30" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
     <col width="12" customWidth="1" min="46" max="46"/>
-    <col width="12" customWidth="1" min="47" max="47"/>
-    <col width="10" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="30" customWidth="1" min="50" max="50"/>
-    <col width="6" customWidth="1" min="51" max="51"/>
-    <col width="10" customWidth="1" min="52" max="52"/>
-    <col width="16" customWidth="1" min="53" max="53"/>
-    <col width="7" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="14" customWidth="1" min="51" max="51"/>
+    <col width="30" customWidth="1" min="52" max="52"/>
+    <col width="6" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="7" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -623,140 +625,150 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>【退款1】退款账号</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>【退款1】退款人</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>超时费合计</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>赔偿合计</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>减免合计</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>隐藏订单</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>应分账金额</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>实分账金额</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>待分账金额</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>业务</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>门店</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>电话</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>顾客openid</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>收款方式</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>支付账号</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>订单号</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>业务日期</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>业务时间</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>结算日期</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>结算时间</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>支付总金额</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>退款总金额</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>订单结余</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>店员姓名</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>店员openid</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>测试</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>临时订单</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>正/闭</t>
         </is>
@@ -809,92 +821,92 @@
       </c>
       <c r="T2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
-      <c r="AA2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC2" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD2" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>苍杰（个人）</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>18601197897</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>HB_ZL_251019_00001</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="n">
+      <c r="AR2" s="2" t="n">
         <v>45949</v>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>20:17:37</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AV2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AW2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>苍杰（个人）</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>oHdTn5Wlwy37YA6kmJP6zE9AoTlI</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>苍杰（个人）</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>关闭</t>
         </is>
@@ -998,110 +1010,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>0</v>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="AE3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>陈女士</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>13691418768</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>oHdTn5YXwygrEnQwYUpwTIV_iRwE</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00002</t>
         </is>
       </c>
-      <c r="AP3" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AR3" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>15:57:03</t>
         </is>
       </c>
-      <c r="AR3" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>16:00:13</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>陈女士</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1205,110 +1227,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>0</v>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="AE4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>汪</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>18612598088</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00003</t>
         </is>
       </c>
-      <c r="AP4" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AR4" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS4" t="inlineStr">
         <is>
           <t>16:07:17</t>
         </is>
       </c>
-      <c r="AR4" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>16:09:12</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>汪</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1412,110 +1444,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>0</v>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
       </c>
       <c r="AC5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="AE5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>18612472341</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00004</t>
         </is>
       </c>
-      <c r="AP5" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AR5" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS5" t="inlineStr">
         <is>
           <t>16:11:37</t>
         </is>
       </c>
-      <c r="AR5" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>16:14:06</t>
         </is>
       </c>
-      <c r="AT5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>汪树泉</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1619,110 +1661,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0</v>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
       </c>
       <c r="AC6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="AE6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>18612472341</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00006</t>
         </is>
       </c>
-      <c r="AP6" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="AR6" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS6" t="inlineStr">
         <is>
           <t>16:15:21</t>
         </is>
       </c>
-      <c r="AR6" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AT6" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>16:19:29</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>汪树泉</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -1826,110 +1878,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>0</v>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
       </c>
       <c r="AC7" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>18612472341</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00007</t>
         </is>
       </c>
-      <c r="AP7" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AR7" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS7" t="inlineStr">
         <is>
           <t>16:16:24</t>
         </is>
       </c>
-      <c r="AR7" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AT7" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>16:20:28</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>汪树泉</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2033,110 +2095,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>0</v>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>宋宏佼</t>
+        </is>
       </c>
       <c r="AC8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="AE8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AH8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>汪</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>18612598088</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00008</t>
         </is>
       </c>
-      <c r="AP8" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="AR8" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS8" t="inlineStr">
         <is>
           <t>16:32:21</t>
         </is>
       </c>
-      <c r="AR8" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AT8" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>16:37:03</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>宋宏佼</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>oHdTn5edMxhoKhq-nwxmAOMwf8LE</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>汪</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2240,110 +2312,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>0</v>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
       </c>
       <c r="AC9" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD9" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF9" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>18612472341</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00009</t>
         </is>
       </c>
-      <c r="AP9" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="AR9" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS9" t="inlineStr">
         <is>
           <t>16:36:19</t>
         </is>
       </c>
-      <c r="AR9" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AT9" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>16:39:42</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>汪树泉</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2447,110 +2529,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>0</v>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
       </c>
       <c r="AC10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="AE10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>汪</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>18612598088</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00010</t>
         </is>
       </c>
-      <c r="AP10" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="AR10" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS10" t="inlineStr">
         <is>
           <t>16:50:26</t>
         </is>
       </c>
-      <c r="AR10" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AT10" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU10" t="inlineStr">
         <is>
           <t>16:51:45</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>汪</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2654,110 +2746,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>0</v>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
       </c>
       <c r="AC11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="AE11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>18612472341</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00011</t>
         </is>
       </c>
-      <c r="AP11" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="AR11" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS11" t="inlineStr">
         <is>
           <t>16:53:13</t>
         </is>
       </c>
-      <c r="AR11" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AT11" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU11" t="inlineStr">
         <is>
           <t>16:56:20</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>汪树泉</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -2838,102 +2940,102 @@
         </is>
       </c>
       <c r="Y12" s="3" t="n"/>
-      <c r="AA12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC12" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD12" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AH12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>18612472341</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00012</t>
         </is>
       </c>
-      <c r="AP12" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="AR12" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS12" t="inlineStr">
         <is>
           <t>16:59:25</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AV12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AW12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>汪树泉</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3037,110 +3139,120 @@
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AA13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="3" t="n">
-        <v>0</v>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
       </c>
       <c r="AC13" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD13" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AH13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>18612472341</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AN13" t="inlineStr">
         <is>
           <t>oHdTn5XtBC8eoSTkoQ0inWnwCUjo</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>1636313350</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
           <t>HB_ZL_251114_00013</t>
         </is>
       </c>
-      <c r="AP13" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AQ13" t="inlineStr">
+      <c r="AR13" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AS13" t="inlineStr">
         <is>
           <t>17:02:45</t>
         </is>
       </c>
-      <c r="AR13" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AT13" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>17:05:36</t>
         </is>
       </c>
-      <c r="AT13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU13" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AV13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AW13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>汪树泉</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>oHdTn5WNHJbS8S6iK97uKLsP9Kss</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>张新健</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr">
+      <c r="BD13" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3201,92 +3313,92 @@
       </c>
       <c r="T14" s="3" t="n"/>
       <c r="Y14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AD14" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AH14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>租赁</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
         <is>
           <t>怀北</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>张小飞（个人）</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>15731361444</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t>oHdTn5d0Mc5njwtCl_bZ8mILaHXM</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>HB_ZL_260111_00001</t>
         </is>
       </c>
-      <c r="AP14" s="2" t="n">
+      <c r="AR14" s="2" t="n">
         <v>46033</v>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>10:38:37</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AV14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AW14" t="inlineStr">
+      <c r="AW14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>李源</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>oHdTn5ULxEoUc3FWTsTxECiJUOzA</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="BA14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BA14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>张小飞（个人）</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr">
+      <c r="BD14" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
@@ -3303,7 +3415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3320,6 +3432,8 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3393,6 +3507,16 @@
           <t>退款1方式</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>退款1账号</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>退款1退款人</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3455,6 +3579,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3517,6 +3651,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3579,6 +3723,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3641,6 +3795,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3703,6 +3867,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3765,6 +3939,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>宋宏佼</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3827,6 +4011,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3889,6 +4083,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3951,6 +4155,16 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4055,6 +4269,16 @@
       <c r="N12" t="inlineStr">
         <is>
           <t>微信支付</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1636313350</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4080,6 +4304,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4123,6 +4348,11 @@
           <t>时间</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4163,6 +4393,11 @@
           <t>15:58:09</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4203,6 +4438,11 @@
           <t>16:00:13</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4243,6 +4483,11 @@
           <t>16:08:15</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4283,6 +4528,11 @@
           <t>16:09:12</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4323,6 +4573,11 @@
           <t>16:12:25</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4363,6 +4618,11 @@
           <t>16:14:06</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4403,6 +4663,11 @@
           <t>16:16:41</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4443,6 +4708,11 @@
           <t>16:17:33</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4483,6 +4753,11 @@
           <t>16:19:29</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4523,6 +4798,11 @@
           <t>16:20:28</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4563,6 +4843,11 @@
           <t>16:33:52</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>宋宏佼</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4603,6 +4888,11 @@
           <t>16:37:03</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>宋宏佼</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4643,6 +4933,11 @@
           <t>16:38:16</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4683,6 +4978,11 @@
           <t>16:39:42</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4723,6 +5023,11 @@
           <t>16:51:11</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4763,6 +5068,11 @@
           <t>16:51:45</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>张新健</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4803,6 +5113,11 @@
           <t>16:55:23</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4843,6 +5158,11 @@
           <t>16:56:20</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4883,6 +5203,11 @@
           <t>17:01:09</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4923,6 +5248,11 @@
           <t>17:04:56</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4961,6 +5291,11 @@
       <c r="H22" t="inlineStr">
         <is>
           <t>17:05:36</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>汪树泉</t>
         </is>
       </c>
     </row>
